--- a/data/trans_orig/P17E-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2007</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31928</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>27121</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50633</t>
+          <t>48405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47573</t>
+          <t>46665</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73725</t>
+          <t>74587</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95046</t>
+          <t>95804</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111515</t>
+          <t>112066</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>163468</t>
+          <t>165696</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>187220</t>
+          <t>186980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>267351</t>
+          <t>266489</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>293503</t>
+          <t>294411</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33624</t>
+          <t>32583</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47148</t>
+          <t>47354</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76124</t>
+          <t>75359</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67875</t>
+          <t>67176</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102735</t>
+          <t>101393</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>158728</t>
+          <t>159769</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>177527</t>
+          <t>178048</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>231295</t>
+          <t>232060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>260271</t>
+          <t>260065</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>397036</t>
+          <t>398378</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>431896</t>
+          <t>432595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>27793</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50832</t>
+          <t>50018</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34761</t>
+          <t>35058</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>58304</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70011</t>
+          <t>69997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100015</t>
+          <t>98561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93817</t>
+          <t>94631</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117539</t>
+          <t>116856</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141550</t>
+          <t>140848</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164391</t>
+          <t>164094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>243786</t>
+          <t>245240</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273790</t>
+          <t>273804</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36148</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59360</t>
+          <t>59179</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53708</t>
+          <t>53700</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83779</t>
+          <t>83145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97412</t>
+          <t>95275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136051</t>
+          <t>133104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135966</t>
+          <t>136147</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159178</t>
+          <t>159718</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>243918</t>
+          <t>244552</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273989</t>
+          <t>273997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>386972</t>
+          <t>389919</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>425611</t>
+          <t>427748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,78%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>112176</t>
+          <t>110379</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>151915</t>
+          <t>151942</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>182290</t>
+          <t>186456</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>238856</t>
+          <t>238596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>309304</t>
+          <t>307022</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>375223</t>
+          <t>373086</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>507387</t>
+          <t>507360</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>547126</t>
+          <t>548923</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>809514</t>
+          <t>809774</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>866080</t>
+          <t>861914</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1332449</t>
+          <t>1334586</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1398368</t>
+          <t>1400650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2012</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2012 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28421</t>
+          <t>28332</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51014</t>
+          <t>51806</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26669</t>
+          <t>26684</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47953</t>
+          <t>48800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61073</t>
+          <t>60833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93124</t>
+          <t>93262</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>127625</t>
+          <t>126833</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>150218</t>
+          <t>150307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>189177</t>
+          <t>188330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>210461</t>
+          <t>210446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>322645</t>
+          <t>322507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>354696</t>
+          <t>354936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>33625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58425</t>
+          <t>58082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47160</t>
+          <t>46853</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76328</t>
+          <t>77478</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89213</t>
+          <t>87960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127161</t>
+          <t>126898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179195</t>
+          <t>179538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204923</t>
+          <t>203995</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>279686</t>
+          <t>278536</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>308854</t>
+          <t>309161</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>466473</t>
+          <t>466736</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>504421</t>
+          <t>505674</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,18%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27829</t>
+          <t>27101</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51943</t>
+          <t>52396</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34182</t>
+          <t>33583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58327</t>
+          <t>58643</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68458</t>
+          <t>67932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104402</t>
+          <t>102502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124468</t>
+          <t>124015</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148582</t>
+          <t>149310</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172153</t>
+          <t>171837</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>196298</t>
+          <t>196897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>302489</t>
+          <t>304389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>338433</t>
+          <t>338959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,3%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29431</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52833</t>
+          <t>53384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55483</t>
+          <t>55395</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84957</t>
+          <t>85394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92518</t>
+          <t>94334</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132796</t>
+          <t>132992</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134637</t>
+          <t>134086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158039</t>
+          <t>157168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>244883</t>
+          <t>244446</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274357</t>
+          <t>274445</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>384514</t>
+          <t>384318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>424792</t>
+          <t>422976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139462</t>
+          <t>141433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187798</t>
+          <t>187992</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187618</t>
+          <t>188703</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>240049</t>
+          <t>241434</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>341123</t>
+          <t>341360</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>415989</t>
+          <t>409593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>592342</t>
+          <t>592148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>640678</t>
+          <t>638707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>913415</t>
+          <t>912030</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>965846</t>
+          <t>964761</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1517615</t>
+          <t>1524011</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1592481</t>
+          <t>1592244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2016</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2016 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39834</t>
+          <t>40048</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40646</t>
+          <t>39627</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66143</t>
+          <t>66094</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66095</t>
+          <t>65013</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98131</t>
+          <t>98121</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>153365</t>
+          <t>153151</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>173423</t>
+          <t>173413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>181835</t>
+          <t>181884</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>207332</t>
+          <t>208351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>343046</t>
+          <t>343056</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>375082</t>
+          <t>376164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,26%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29398</t>
+          <t>27903</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54365</t>
+          <t>52826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36512</t>
+          <t>37437</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64880</t>
+          <t>63740</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71005</t>
+          <t>71378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109168</t>
+          <t>108837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>211261</t>
+          <t>212800</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>236228</t>
+          <t>237723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289944</t>
+          <t>291084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>318312</t>
+          <t>317387</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>511282</t>
+          <t>511613</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>549445</t>
+          <t>549072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30536</t>
+          <t>30561</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55766</t>
+          <t>54752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51483</t>
+          <t>48980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79075</t>
+          <t>78964</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89048</t>
+          <t>87435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124339</t>
+          <t>126193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>120014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144230</t>
+          <t>144205</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171913</t>
+          <t>172024</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>199505</t>
+          <t>202008</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301415</t>
+          <t>299561</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>336706</t>
+          <t>338319</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,46%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35986</t>
+          <t>35630</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61901</t>
+          <t>60047</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41679</t>
+          <t>42276</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70091</t>
+          <t>71731</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82655</t>
+          <t>83355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120973</t>
+          <t>121886</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156141</t>
+          <t>157995</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182056</t>
+          <t>182412</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>240439</t>
+          <t>238799</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268851</t>
+          <t>268254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>407600</t>
+          <t>406687</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>445918</t>
+          <t>445218</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>133518</t>
+          <t>133418</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>178957</t>
+          <t>181224</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196249</t>
+          <t>193700</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>251235</t>
+          <t>247380</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>341478</t>
+          <t>343729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>411442</t>
+          <t>418287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>672677</t>
+          <t>670410</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>718116</t>
+          <t>718216</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>913085</t>
+          <t>916940</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>968071</t>
+          <t>970620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1604511</t>
+          <t>1597666</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1674475</t>
+          <t>1672224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2023</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13012</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27419</t>
+          <t>27455</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21657</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>37363</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37267</t>
+          <t>37704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59673</t>
+          <t>59272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85689</t>
+          <t>85653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99991</t>
+          <t>100096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129690</t>
+          <t>130720</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>146426</t>
+          <t>147199</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221518</t>
+          <t>221919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243924</t>
+          <t>243487</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>26636</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48786</t>
+          <t>49344</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34921</t>
+          <t>35979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57720</t>
+          <t>58356</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67927</t>
+          <t>68245</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100269</t>
+          <t>99267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>134322</t>
+          <t>133764</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156617</t>
+          <t>156472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>159325</t>
+          <t>158689</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182124</t>
+          <t>181066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>299884</t>
+          <t>300886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>332226</t>
+          <t>331908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32926</t>
+          <t>32342</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56051</t>
+          <t>57581</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28705</t>
+          <t>28703</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46268</t>
+          <t>47154</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66109</t>
+          <t>66690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95166</t>
+          <t>95356</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77614</t>
+          <t>76084</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100739</t>
+          <t>101323</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102514</t>
+          <t>101628</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120077</t>
+          <t>120079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>187281</t>
+          <t>187091</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>216338</t>
+          <t>215757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,39%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43178</t>
+          <t>41878</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67868</t>
+          <t>65902</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45724</t>
+          <t>45771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107969</t>
+          <t>108992</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91210</t>
+          <t>92120</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166397</t>
+          <t>164121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141079</t>
+          <t>143045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165769</t>
+          <t>167069</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>253958</t>
+          <t>252935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>316203</t>
+          <t>316156</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>404477</t>
+          <t>406753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>479664</t>
+          <t>478754</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132227</t>
+          <t>132158</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>174862</t>
+          <t>178224</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>144797</t>
+          <t>149534</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220225</t>
+          <t>219688</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>290101</t>
+          <t>295990</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>382749</t>
+          <t>383975</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463966</t>
+          <t>460604</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>506601</t>
+          <t>506670</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>675612</t>
+          <t>676149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>751040</t>
+          <t>746303</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1151916</t>
+          <t>1150690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1244564</t>
+          <t>1238675</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P17E-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14908</t>
+          <t>15495</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31170</t>
+          <t>32316</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27121</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48405</t>
+          <t>50040</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46665</t>
+          <t>47474</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74587</t>
+          <t>78217</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95804</t>
+          <t>94658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112066</t>
+          <t>111479</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>165696</t>
+          <t>164061</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186980</t>
+          <t>187396</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>266489</t>
+          <t>262859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>294411</t>
+          <t>293602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14304</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32583</t>
+          <t>33698</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47354</t>
+          <t>47860</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75359</t>
+          <t>76005</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67176</t>
+          <t>66615</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101393</t>
+          <t>102121</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159769</t>
+          <t>158654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>178048</t>
+          <t>177162</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>232060</t>
+          <t>231414</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>260065</t>
+          <t>259559</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>398378</t>
+          <t>397650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>432595</t>
+          <t>433156</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27793</t>
+          <t>27615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50018</t>
+          <t>48729</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35058</t>
+          <t>35565</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58304</t>
+          <t>58363</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69997</t>
+          <t>69116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98561</t>
+          <t>99342</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94631</t>
+          <t>95920</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116856</t>
+          <t>117034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140848</t>
+          <t>140789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164094</t>
+          <t>163587</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245240</t>
+          <t>244459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273804</t>
+          <t>274685</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35608</t>
+          <t>36014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59179</t>
+          <t>59110</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53700</t>
+          <t>54154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83145</t>
+          <t>83503</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95275</t>
+          <t>96489</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133104</t>
+          <t>132887</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136147</t>
+          <t>136216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159718</t>
+          <t>159312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>244552</t>
+          <t>244194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273997</t>
+          <t>273543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>389919</t>
+          <t>390136</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>427748</t>
+          <t>426534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110379</t>
+          <t>111032</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>151942</t>
+          <t>151224</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>186456</t>
+          <t>187574</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>238596</t>
+          <t>237650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>307022</t>
+          <t>306808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>373086</t>
+          <t>373335</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>507360</t>
+          <t>508078</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>548923</t>
+          <t>548270</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>809774</t>
+          <t>810720</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>861914</t>
+          <t>860796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1334586</t>
+          <t>1334337</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1400650</t>
+          <t>1400864</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28332</t>
+          <t>28252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51806</t>
+          <t>51437</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>26587</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48800</t>
+          <t>49085</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60833</t>
+          <t>59333</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93262</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126833</t>
+          <t>127202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>150307</t>
+          <t>150387</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>188330</t>
+          <t>188045</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>210446</t>
+          <t>210543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>322507</t>
+          <t>324238</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>354936</t>
+          <t>356436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33625</t>
+          <t>31954</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58082</t>
+          <t>56964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46853</t>
+          <t>47584</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77478</t>
+          <t>76751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87960</t>
+          <t>88693</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126898</t>
+          <t>126086</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179538</t>
+          <t>180656</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203995</t>
+          <t>205666</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>278536</t>
+          <t>279263</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>309161</t>
+          <t>308430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>466736</t>
+          <t>467548</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>505674</t>
+          <t>504941</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27101</t>
+          <t>28409</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52396</t>
+          <t>53638</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33583</t>
+          <t>34393</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58643</t>
+          <t>58938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67932</t>
+          <t>66872</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102502</t>
+          <t>101408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124015</t>
+          <t>122773</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149310</t>
+          <t>148002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171837</t>
+          <t>171542</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>196897</t>
+          <t>196087</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>304389</t>
+          <t>305483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>338959</t>
+          <t>340019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,57%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53384</t>
+          <t>53132</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55395</t>
+          <t>54519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85394</t>
+          <t>84369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94334</t>
+          <t>92728</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132992</t>
+          <t>131256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134086</t>
+          <t>134338</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157168</t>
+          <t>156946</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>244446</t>
+          <t>245471</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274445</t>
+          <t>275321</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>384318</t>
+          <t>386054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>422976</t>
+          <t>424582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141433</t>
+          <t>142425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187992</t>
+          <t>187611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>188703</t>
+          <t>188036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>241434</t>
+          <t>241797</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>341360</t>
+          <t>339911</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>409593</t>
+          <t>413673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>592148</t>
+          <t>592529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>638707</t>
+          <t>637715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>912030</t>
+          <t>911667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>964761</t>
+          <t>965428</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1524011</t>
+          <t>1519931</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1592244</t>
+          <t>1593693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,42%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19786</t>
+          <t>19826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40048</t>
+          <t>39624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39627</t>
+          <t>39684</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66094</t>
+          <t>65466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65013</t>
+          <t>63623</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98121</t>
+          <t>98520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>153151</t>
+          <t>153575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>173413</t>
+          <t>173373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>181884</t>
+          <t>182512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>208351</t>
+          <t>208294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>343056</t>
+          <t>342657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>376164</t>
+          <t>377554</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27903</t>
+          <t>27896</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52826</t>
+          <t>52963</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37437</t>
+          <t>36536</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63740</t>
+          <t>63151</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71378</t>
+          <t>70762</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108837</t>
+          <t>106833</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212800</t>
+          <t>212663</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>237723</t>
+          <t>237730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>291084</t>
+          <t>291673</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>317387</t>
+          <t>318288</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>511613</t>
+          <t>513617</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>549072</t>
+          <t>549688</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,59%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30561</t>
+          <t>30916</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54752</t>
+          <t>54231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48980</t>
+          <t>51987</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78964</t>
+          <t>79890</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87435</t>
+          <t>87253</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126193</t>
+          <t>125383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120014</t>
+          <t>120535</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144205</t>
+          <t>143850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172024</t>
+          <t>171098</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202008</t>
+          <t>199001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>299561</t>
+          <t>300371</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>338319</t>
+          <t>338501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35630</t>
+          <t>33702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60047</t>
+          <t>59410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42276</t>
+          <t>43460</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71731</t>
+          <t>71130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83355</t>
+          <t>84129</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121886</t>
+          <t>121181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157995</t>
+          <t>158632</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182412</t>
+          <t>184340</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>238799</t>
+          <t>239400</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268254</t>
+          <t>267070</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>406687</t>
+          <t>407392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>445218</t>
+          <t>444444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>133418</t>
+          <t>133344</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181224</t>
+          <t>180688</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193700</t>
+          <t>193667</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>247380</t>
+          <t>250617</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>343729</t>
+          <t>341072</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>418287</t>
+          <t>415502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>670410</t>
+          <t>670946</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>718216</t>
+          <t>718290</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>916940</t>
+          <t>913703</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>970620</t>
+          <t>970653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1597666</t>
+          <t>1600451</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1672224</t>
+          <t>1674881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27455</t>
+          <t>31030</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>30019</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20884</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37363</t>
+          <t>41354</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>47560</t>
+          <t>51428</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37704</t>
+          <t>40492</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59272</t>
+          <t>64393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93619</t>
+          <t>99351</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85653</t>
+          <t>89730</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100096</t>
+          <t>106930</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>140012</t>
+          <t>149797</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130720</t>
+          <t>138462</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147199</t>
+          <t>157243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>233631</t>
+          <t>249147</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221919</t>
+          <t>236182</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243487</t>
+          <t>260083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,53%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>113108</t>
+          <t>120760</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113108</t>
+          <t>120760</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113108</t>
+          <t>120760</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>168083</t>
+          <t>179816</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>168083</t>
+          <t>179816</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168083</t>
+          <t>179816</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>281191</t>
+          <t>300575</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>281191</t>
+          <t>300575</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>281191</t>
+          <t>300575</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36802</t>
+          <t>40668</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26636</t>
+          <t>29149</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49344</t>
+          <t>55048</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45774</t>
+          <t>50841</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35979</t>
+          <t>40516</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58356</t>
+          <t>63727</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>82576</t>
+          <t>91510</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68245</t>
+          <t>75787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99267</t>
+          <t>109900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>146306</t>
+          <t>162436</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133764</t>
+          <t>148056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156472</t>
+          <t>173955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>171271</t>
+          <t>194686</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>158689</t>
+          <t>181800</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181066</t>
+          <t>205011</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>317577</t>
+          <t>357121</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>300886</t>
+          <t>338731</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>331908</t>
+          <t>372844</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,11%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>183108</t>
+          <t>203104</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>183108</t>
+          <t>203104</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>183108</t>
+          <t>203104</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>217045</t>
+          <t>245527</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>217045</t>
+          <t>245527</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>217045</t>
+          <t>245527</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>400153</t>
+          <t>448631</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>400153</t>
+          <t>448631</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>400153</t>
+          <t>448631</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>43489</t>
+          <t>47681</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>35720</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57581</t>
+          <t>61242</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36671</t>
+          <t>47527</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28703</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47154</t>
+          <t>58785</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>80160</t>
+          <t>95208</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66690</t>
+          <t>79422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95356</t>
+          <t>113586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90176</t>
+          <t>98652</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76084</t>
+          <t>85091</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101323</t>
+          <t>110613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>112111</t>
+          <t>132227</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101628</t>
+          <t>120969</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120079</t>
+          <t>143297</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>202287</t>
+          <t>230878</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>187091</t>
+          <t>212500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>215757</t>
+          <t>246664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>133665</t>
+          <t>146333</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133665</t>
+          <t>146333</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>133665</t>
+          <t>146333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>148782</t>
+          <t>179754</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148782</t>
+          <t>179754</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148782</t>
+          <t>179754</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>282447</t>
+          <t>326086</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>282447</t>
+          <t>326086</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>282447</t>
+          <t>326086</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54020</t>
+          <t>57552</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41878</t>
+          <t>44860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65902</t>
+          <t>71325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>83076</t>
+          <t>91406</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45771</t>
+          <t>76693</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108992</t>
+          <t>105784</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>137096</t>
+          <t>148958</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92120</t>
+          <t>130790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164121</t>
+          <t>168846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>154927</t>
+          <t>160221</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143045</t>
+          <t>146448</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167069</t>
+          <t>172913</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>278851</t>
+          <t>229330</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>252935</t>
+          <t>214952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>316156</t>
+          <t>244043</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>433778</t>
+          <t>389551</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>406753</t>
+          <t>369663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>478754</t>
+          <t>407719</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>75,71%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>208947</t>
+          <t>217773</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>208947</t>
+          <t>217773</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>208947</t>
+          <t>217773</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>361927</t>
+          <t>320736</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>361927</t>
+          <t>320736</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>361927</t>
+          <t>320736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>570874</t>
+          <t>538509</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>570874</t>
+          <t>538509</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>570874</t>
+          <t>538509</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>153801</t>
+          <t>167311</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132158</t>
+          <t>146418</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>178224</t>
+          <t>194015</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>193591</t>
+          <t>219793</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>149534</t>
+          <t>196315</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>219688</t>
+          <t>243175</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>347392</t>
+          <t>387104</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>295990</t>
+          <t>355774</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>383975</t>
+          <t>422041</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>485027</t>
+          <t>520658</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>460604</t>
+          <t>493954</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>506670</t>
+          <t>541551</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>702246</t>
+          <t>706040</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>676149</t>
+          <t>682658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746303</t>
+          <t>729518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1187273</t>
+          <t>1226698</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1150690</t>
+          <t>1191761</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1238675</t>
+          <t>1258028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>638828</t>
+          <t>687969</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>638828</t>
+          <t>687969</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>638828</t>
+          <t>687969</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>895837</t>
+          <t>925833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>895837</t>
+          <t>925833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>895837</t>
+          <t>925833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1534665</t>
+          <t>1613802</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1534665</t>
+          <t>1613802</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1534665</t>
+          <t>1613802</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P17E-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Habitat-trans_orig.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1860,7 +1860,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2203,7 +2203,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2778,7 +2778,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -3121,7 +3121,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3464,7 +3464,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3807,7 +3807,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -5411,7 +5411,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -6672,7 +6672,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7015,7 +7015,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -7358,7 +7358,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -7701,7 +7701,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -8044,7 +8044,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
